--- a/survey_templates/025_holiday_trivia_quiz--survey_templates.xlsx
+++ b/survey_templates/025_holiday_trivia_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>welcome_to_holiday_trivia_quiz</t>
+          <t>Welcome to Holiday Trivia Quiz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_your_favorite_holiday</t>
+          <t>What is your favorite holiday?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,10 +571,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Choose your answer above</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +588,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>score_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>score_1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is known for being the largest holiday celebration in the world?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +620,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>answer_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_do_you_know</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Answer 2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Your answers are above</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,12 +647,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>Which holiday is celebrated in March?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +665,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>What is the traditional color associated with St. Patrick's Day?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +688,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_do_you_know_2</t>
+          <t>What is the primary reason for the 4th of July?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +716,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>Which holiday is celebrated with trick-or-treating?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +734,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what_do_you_know_3</t>
+          <t>What is the primary reason for Christmas?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +757,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>Which of the following holidays is not a typical New Year's Day activity?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +813,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +836,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,218 +882,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>question_5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>answer_5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>answer_5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_6</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>question_6</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>answer_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>answer_6</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>answer_7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>answer_7</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>answer_8</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>answer_8</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +903,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +936,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'christmas'}</t>
+          <t>christmas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Christmas'}</t>
+          <t>Christmas</t>
         </is>
       </c>
     </row>
@@ -1148,12 +953,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'halloween'}</t>
+          <t>halloween</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Halloween'}</t>
+          <t>Halloween</t>
         </is>
       </c>
     </row>
@@ -1165,12 +970,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'easter'}</t>
+          <t>easter</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Easter'}</t>
+          <t>Easter</t>
         </is>
       </c>
     </row>
@@ -1182,12 +987,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1004,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1021,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1038,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>christmas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Christmas</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1055,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>new_year's_eve</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>New Year's Eve</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1072,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>easter_sunday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Easter Sunday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1089,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1106,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1123,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1140,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>st._patrick's_day</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>St. Patrick's Day</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1157,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>easter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Easter</t>
         </is>
       </c>
     </row>
@@ -1369,624 +1174,267 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>april_fools'_day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>April Fools' Day</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>independence_day</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Independence Day</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>labor_day</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Labor Day</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>summer_solstice</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Summer Solstice</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>halloween</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Halloween</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>thanksgiving</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>easter</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Easter</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>gift-giving</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Gift-giving</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>family_reunions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Family reunions</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>religious_celebrations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Religious celebrations</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>answer_5_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>counting_down_to_the_new_year</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Counting down to the new year</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>answer_5_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>watching_the_super_bowl</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Watching the Super Bowl</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>answer_5_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>watching_fireworks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>answer_7_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>answer_7_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>answer_7_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>answer_8_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>answer_8_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>answer_8_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Watching fireworks</t>
         </is>
       </c>
     </row>
